--- a/data/trans_dic/IP04F-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente</t>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -583,7 +584,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,39 +632,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 25,31</t>
+          <t>10,0; 26,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 21,88</t>
+          <t>8,21; 22,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,01; 19,64</t>
+          <t>5,77; 20,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 21,0</t>
+          <t>7,3; 20,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 19,41</t>
+          <t>8,87; 19,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 18,72</t>
+          <t>8,8; 18,22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -711,39 +712,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 12,78</t>
+          <t>3,8; 11,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,92</t>
+          <t>1,75; 8,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,51</t>
+          <t>2,35; 9,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,44</t>
+          <t>1,23; 6,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,36</t>
+          <t>4,08; 9,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,23</t>
+          <t>1,92; 6,44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 19,83</t>
+          <t>7,11; 19,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,35</t>
+          <t>2,26; 12,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 16,91</t>
+          <t>5,59; 17,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 16,68</t>
+          <t>4,17; 16,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 16,4</t>
+          <t>7,81; 16,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,72</t>
+          <t>3,73; 11,29</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,51</t>
+          <t>2,61; 13,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,54</t>
+          <t>3,24; 12,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,88</t>
+          <t>0,8; 7,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,84</t>
+          <t>0,91; 8,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,25</t>
+          <t>2,37; 8,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 8,63</t>
+          <t>3,0; 9,07</t>
         </is>
       </c>
     </row>
@@ -951,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 18,9</t>
+          <t>4,66; 19,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 16,98</t>
+          <t>3,12; 16,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 20,19</t>
+          <t>4,93; 21,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,4</t>
+          <t>2,68; 15,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 16,5</t>
+          <t>5,66; 17,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 13,85</t>
+          <t>3,8; 13,52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1031,39 +1032,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 19,36</t>
+          <t>5,67; 21,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,1; 25,44</t>
+          <t>9,06; 25,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 14,8</t>
+          <t>3,53; 14,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 13,87</t>
+          <t>2,57; 13,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 14,27</t>
+          <t>5,51; 14,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,71; 16,89</t>
+          <t>6,44; 17,35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1111,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 15,37</t>
+          <t>6,73; 15,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,76; 17,41</t>
+          <t>7,51; 16,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 14,45</t>
+          <t>5,93; 14,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,12</t>
+          <t>6,48; 15,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,2</t>
+          <t>7,18; 13,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,94; 14,32</t>
+          <t>8,1; 14,48</t>
         </is>
       </c>
     </row>
@@ -1191,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 15,56</t>
+          <t>7,67; 15,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,34; 12,03</t>
+          <t>5,26; 12,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,77; 17,54</t>
+          <t>8,55; 16,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,45</t>
+          <t>6,07; 12,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,16; 14,82</t>
+          <t>9,31; 14,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,33</t>
+          <t>6,37; 11,46</t>
         </is>
       </c>
     </row>
@@ -1271,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,31</t>
+          <t>8,59; 12,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,93</t>
+          <t>7,26; 10,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,87</t>
+          <t>7,31; 10,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,55</t>
+          <t>6,22; 9,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,16</t>
+          <t>8,47; 11,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,73</t>
+          <t>7,24; 9,55</t>
         </is>
       </c>
     </row>
@@ -1325,4 +1326,1182 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9235</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7697</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7271</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8293</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16506</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15990</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5570; 14903</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4628; 12763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3737; 13006</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4707; 13353</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10686; 23822</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10631; 22018</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7511</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4071</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13575</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7505</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3980; 12479</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1810; 8430</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2615; 10644</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1332; 7151</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8813; 21014</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4058; 13618</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8564</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3817</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7438</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5963</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16002</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4850; 13578</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1514; 8386</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3980; 12252</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2912; 11823</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10892; 22937</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5095; 15432</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7468</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2030; 10489</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2458; 9398</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>651; 5884</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721; 6723</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3778; 13494</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4643; 14054</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3482</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6611</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2044; 8701</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1336; 7157</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2307; 9834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1226; 7300</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5133; 15503</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3365; 11970</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8636</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4480</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10833</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12431</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>3132; 11740</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4919; 13938</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2098; 8527</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1483; 8053</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>6328; 17175</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>7215; 19432</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>13968</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>15901</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13692</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14624</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>27660</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>30525</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>9227; 21594</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10316; 23150</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8560; 20692</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9296; 21819</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>20217; 37260</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>22739; 40663</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>13465</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20979</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>15567</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>38965</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>29032</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>12389; 25744</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>8577; 19815</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>14534; 28344</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>10295; 21833</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>30854; 48118</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>21202; 38113</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>73130</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>62296</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>140364</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>119913</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>60499; 87864</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>50824; 75219</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>54791; 79969</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>45900; 69992</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>123057; 160411</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>104068; 137380</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04F-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Provincia-trans_dic.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,0; 26,76</t>
+          <t>9,94; 26,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 22,65</t>
+          <t>7,87; 21,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 20,07</t>
+          <t>5,39; 19,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 20,71</t>
+          <t>7,39; 20,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 19,77</t>
+          <t>9,15; 19,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,22</t>
+          <t>8,92; 19,02</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 11,92</t>
+          <t>3,74; 12,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,16</t>
+          <t>1,57; 8,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 9,58</t>
+          <t>2,84; 9,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,61</t>
+          <t>1,23; 6,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 9,73</t>
+          <t>3,89; 9,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,44</t>
+          <t>1,85; 6,08</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 19,91</t>
+          <t>6,5; 20,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 12,55</t>
+          <t>2,18; 12,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,59; 17,2</t>
+          <t>5,64; 17,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 16,91</t>
+          <t>4,12; 15,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 16,45</t>
+          <t>7,54; 16,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 11,29</t>
+          <t>4,28; 12,63</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 13,49</t>
+          <t>2,96; 13,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 12,4</t>
+          <t>3,28; 12,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,19</t>
+          <t>0,81; 8,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,49</t>
+          <t>0,93; 8,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,46</t>
+          <t>2,41; 8,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,07</t>
+          <t>2,71; 8,95</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 19,82</t>
+          <t>3,2; 18,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 16,7</t>
+          <t>3,11; 18,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 21,03</t>
+          <t>5,29; 21,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,98</t>
+          <t>2,58; 15,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 17,1</t>
+          <t>5,77; 16,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,52</t>
+          <t>3,78; 13,46</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,67; 21,23</t>
+          <t>5,32; 20,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,06; 25,68</t>
+          <t>8,99; 24,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,53; 14,34</t>
+          <t>3,37; 15,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 13,95</t>
+          <t>2,5; 14,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 14,97</t>
+          <t>5,23; 14,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,44; 17,35</t>
+          <t>7,0; 16,85</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,76</t>
+          <t>6,29; 15,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 16,85</t>
+          <t>7,44; 16,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,33</t>
+          <t>6,03; 13,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 15,22</t>
+          <t>6,27; 15,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 13,24</t>
+          <t>7,33; 12,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,48</t>
+          <t>8,01; 14,11</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 15,95</t>
+          <t>7,63; 16,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 12,15</t>
+          <t>5,16; 12,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,55; 16,68</t>
+          <t>8,48; 17,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,87</t>
+          <t>6,19; 13,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,31; 14,52</t>
+          <t>9,26; 15,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,46</t>
+          <t>6,62; 11,47</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,48</t>
+          <t>8,75; 12,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,26; 10,75</t>
+          <t>7,2; 10,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,67</t>
+          <t>7,37; 10,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,48</t>
+          <t>6,36; 9,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,04</t>
+          <t>8,49; 11,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,55</t>
+          <t>7,27; 9,75</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5570; 14903</t>
+          <t>5538; 14599</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4628; 12763</t>
+          <t>4436; 12278</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3737; 13006</t>
+          <t>3492; 12401</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4707; 13353</t>
+          <t>4767; 13359</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10686; 23822</t>
+          <t>11024; 23621</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10631; 22018</t>
+          <t>10773; 22978</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3980; 12479</t>
+          <t>3914; 12709</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1810; 8430</t>
+          <t>1618; 8345</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2615; 10644</t>
+          <t>3156; 11090</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1332; 7151</t>
+          <t>1328; 7558</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8813; 21014</t>
+          <t>8391; 20194</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4058; 13618</t>
+          <t>3912; 12864</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4850; 13578</t>
+          <t>4431; 13838</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1514; 8386</t>
+          <t>1456; 8575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3980; 12252</t>
+          <t>4016; 12452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2912; 11823</t>
+          <t>2880; 11030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10892; 22937</t>
+          <t>10511; 23309</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5095; 15432</t>
+          <t>5854; 17276</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2030; 10489</t>
+          <t>2302; 10652</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2458; 9398</t>
+          <t>2485; 9842</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>651; 5884</t>
+          <t>661; 6688</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>721; 6723</t>
+          <t>735; 7030</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3778; 13494</t>
+          <t>3849; 13372</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4643; 14054</t>
+          <t>4198; 13867</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2044; 8701</t>
+          <t>1406; 8276</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1336; 7157</t>
+          <t>1333; 7840</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2307; 9834</t>
+          <t>2474; 10113</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1226; 7300</t>
+          <t>1179; 6981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5133; 15503</t>
+          <t>5233; 14886</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3365; 11970</t>
+          <t>3343; 11920</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3132; 11740</t>
+          <t>2944; 11083</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4919; 13938</t>
+          <t>4879; 13396</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2098; 8527</t>
+          <t>2004; 9123</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1483; 8053</t>
+          <t>1441; 8253</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6328; 17175</t>
+          <t>6003; 16604</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7215; 19432</t>
+          <t>7838; 18878</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9227; 21594</t>
+          <t>8622; 20726</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10316; 23150</t>
+          <t>10224; 22842</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8560; 20692</t>
+          <t>8714; 19985</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9296; 21819</t>
+          <t>8995; 22045</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20217; 37260</t>
+          <t>20627; 36327</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22739; 40663</t>
+          <t>22478; 39619</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12389; 25744</t>
+          <t>12312; 26066</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8577; 19815</t>
+          <t>8419; 19901</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14534; 28344</t>
+          <t>14408; 29006</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10295; 21833</t>
+          <t>10492; 22686</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30854; 48118</t>
+          <t>30694; 50308</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21202; 38113</t>
+          <t>22033; 38163</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>60499; 87864</t>
+          <t>61583; 87539</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>50824; 75219</t>
+          <t>50423; 73028</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54791; 79969</t>
+          <t>55270; 80863</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45900; 69992</t>
+          <t>46929; 69529</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>123057; 160411</t>
+          <t>123474; 160610</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>104068; 137380</t>
+          <t>104562; 140196</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04F-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Provincia-trans_dic.xlsx
@@ -520,13 +520,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -594,22 +594,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>16,58%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>13,66%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 26,21</t>
+          <t>6,01; 19,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 21,79</t>
+          <t>7,43; 21,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 19,14</t>
+          <t>9,69; 25,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 20,72</t>
+          <t>7,46; 21,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 19,6</t>
+          <t>8,87; 19,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 19,02</t>
+          <t>8,81; 18,72</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>3,94%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,14</t>
+          <t>2,65; 9,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,08</t>
+          <t>1,21; 7,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,98</t>
+          <t>3,81; 12,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,99</t>
+          <t>1,53; 8,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,35</t>
+          <t>4,0; 9,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,08</t>
+          <t>1,91; 6,23</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>12,56%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 20,3</t>
+          <t>5,62; 16,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,83</t>
+          <t>4,06; 16,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 17,48</t>
+          <t>6,3; 19,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 15,78</t>
+          <t>2,18; 12,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 16,72</t>
+          <t>7,46; 16,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 12,63</t>
+          <t>4,38; 11,72</t>
         </is>
       </c>
     </row>
@@ -834,22 +834,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>6,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,7</t>
+          <t>0,81; 6,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,98</t>
+          <t>0,9; 8,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,18</t>
+          <t>2,91; 12,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,88</t>
+          <t>3,38; 12,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 8,38</t>
+          <t>2,31; 8,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 8,95</t>
+          <t>2,67; 8,63</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>9,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>8,12%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 18,85</t>
+          <t>4,51; 20,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 18,29</t>
+          <t>2,5; 15,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 21,63</t>
+          <t>4,59; 18,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 15,28</t>
+          <t>3,1; 16,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 16,42</t>
+          <t>5,68; 16,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 13,46</t>
+          <t>4,18; 13,85</t>
         </is>
       </c>
     </row>
@@ -994,22 +994,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>11,49%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>15,91%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 20,04</t>
+          <t>3,47; 14,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 24,68</t>
+          <t>2,56; 13,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 15,34</t>
+          <t>5,26; 19,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 14,29</t>
+          <t>9,1; 25,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 14,47</t>
+          <t>5,43; 14,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 16,85</t>
+          <t>6,71; 16,89</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>10,19%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>11,58%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 15,12</t>
+          <t>6,13; 14,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 16,63</t>
+          <t>6,51; 15,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 13,84</t>
+          <t>6,3; 15,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 15,38</t>
+          <t>7,76; 17,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,91</t>
+          <t>7,36; 13,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,01; 14,11</t>
+          <t>7,94; 14,32</t>
         </is>
       </c>
     </row>
@@ -1154,22 +1154,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12,35%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>11,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>8,26%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,63; 16,14</t>
+          <t>8,77; 17,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,21</t>
+          <t>5,98; 13,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,48; 17,07</t>
+          <t>7,46; 15,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 13,38</t>
+          <t>5,34; 12,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,26; 15,18</t>
+          <t>9,16; 14,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 11,47</t>
+          <t>6,47; 11,33</t>
         </is>
       </c>
     </row>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,43</t>
+          <t>7,4; 10,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,43</t>
+          <t>6,4; 9,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,79</t>
+          <t>8,67; 12,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,42</t>
+          <t>7,45; 10,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,05</t>
+          <t>8,43; 11,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,75</t>
+          <t>7,19; 9,73</t>
         </is>
       </c>
     </row>
@@ -1356,13 +1356,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -1430,17 +1430,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7271</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8293</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>9235</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>7697</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7271</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5538; 14599</t>
+          <t>3893; 12732</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4436; 12278</t>
+          <t>4787; 13536</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3492; 12401</t>
+          <t>5399; 14098</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4767; 13359</t>
+          <t>4205; 12332</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11024; 23621</t>
+          <t>10689; 23390</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10773; 22978</t>
+          <t>10642; 22618</t>
         </is>
       </c>
     </row>
@@ -1548,22 +1548,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1586,22 +1586,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>7511</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>4071</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6064</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3914; 12709</t>
+          <t>2943; 10576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1618; 8345</t>
+          <t>1305; 8053</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3156; 11090</t>
+          <t>3985; 13387</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1328; 7558</t>
+          <t>1578; 9215</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8391; 20194</t>
+          <t>8638; 20213</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3912; 12864</t>
+          <t>4046; 13173</t>
         </is>
       </c>
     </row>
@@ -1666,22 +1666,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1704,22 +1704,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7438</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5963</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>8564</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>3817</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7438</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4431; 13838</t>
+          <t>4008; 12052</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1456; 8575</t>
+          <t>2840; 11661</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4016; 12452</t>
+          <t>4298; 13522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2880; 11030</t>
+          <t>1460; 8256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10511; 23309</t>
+          <t>10407; 22873</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5854; 17276</t>
+          <t>5990; 16020</t>
         </is>
       </c>
     </row>
@@ -1784,22 +1784,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1822,22 +1822,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>5306</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>5226</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2162</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2302; 10652</t>
+          <t>661; 5626</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2485; 9842</t>
+          <t>714; 6998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>661; 6688</t>
+          <t>2266; 9727</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>735; 7030</t>
+          <t>2564; 9509</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3849; 13372</t>
+          <t>3683; 13160</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4198; 13867</t>
+          <t>4132; 13376</t>
         </is>
       </c>
     </row>
@@ -1902,17 +1902,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1940,22 +1940,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>4207</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>3482</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5148</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1406; 8276</t>
+          <t>2110; 9441</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1333; 7840</t>
+          <t>1144; 7037</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2474; 10113</t>
+          <t>2017; 8296</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1179; 6981</t>
+          <t>1329; 7280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5233; 14886</t>
+          <t>5150; 14962</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3343; 11920</t>
+          <t>3703; 12261</t>
         </is>
       </c>
     </row>
@@ -2020,22 +2020,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4480</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>6352</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>8636</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4480</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3795</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2944; 11083</t>
+          <t>2064; 8802</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4879; 13396</t>
+          <t>1480; 8011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2004; 9123</t>
+          <t>2908; 10703</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1441; 8253</t>
+          <t>4936; 13809</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6003; 16604</t>
+          <t>6235; 16376</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7838; 18878</t>
+          <t>7520; 18915</t>
         </is>
       </c>
     </row>
@@ -2143,17 +2143,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>13692</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>14624</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>13968</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>15901</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>13692</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>14624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8622; 20726</t>
+          <t>8857; 20875</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10224; 22842</t>
+          <t>9331; 21679</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8714; 19985</t>
+          <t>8628; 21065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8995; 22045</t>
+          <t>10656; 23920</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20627; 36327</t>
+          <t>20712; 37163</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22478; 39619</t>
+          <t>22302; 40214</t>
         </is>
       </c>
     </row>
@@ -2256,22 +2256,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>20979</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15567</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>17986</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>13465</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>20979</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>15567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12312; 26066</t>
+          <t>14895; 29805</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8419; 19901</t>
+          <t>10136; 22815</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14408; 29006</t>
+          <t>12039; 25117</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10492; 22686</t>
+          <t>8700; 19622</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30694; 50308</t>
+          <t>30339; 49092</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22033; 38163</t>
+          <t>21505; 37688</t>
         </is>
       </c>
     </row>
@@ -2374,22 +2374,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2412,22 +2412,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>62296</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>61583; 87539</t>
+          <t>55435; 81500</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>50423; 73028</t>
+          <t>47226; 70514</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55270; 80863</t>
+          <t>61013; 86633</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46929; 69529</t>
+          <t>52170; 76515</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>123474; 160610</t>
+          <t>122576; 162201</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>104562; 140196</t>
+          <t>103401; 139952</t>
         </is>
       </c>
     </row>
